--- a/dataDriven/ExcelFiles/data.xlsx
+++ b/dataDriven/ExcelFiles/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Expleo Pytest\dataDriven\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26C1D4E-534F-4841-9D6C-1E2FAC97AA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8400E0C9-59E4-468B-ADE0-D265948B35E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{227A3A5A-6E4B-4FFA-B298-4A95A8B93ABE}"/>
   </bookViews>
@@ -34,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>Username</t>
-  </si>
-  <si>
-    <t>admin</t>
   </si>
   <si>
     <t>Pass</t>
@@ -408,23 +405,23 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
